--- a/latest.xlsx
+++ b/latest.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>期货信号跟踪台 · 2026-10-29 收盘后</t>
+          <t>期货信号跟踪台 · 2026-10-29 （2026-10-30 早盘）</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>尿素</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>建材</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1820,22 +1820,22 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>5299</v>
+        <v>1716</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>5050</v>
+        <v>1670</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>5299</v>
+        <v>1716</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="N6" s="12">
         <f>ABS(I6-J6)*H6*K6</f>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>尿素</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>建材</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>1716</v>
+        <v>5299</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>1670</v>
+        <v>5050</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>1716</v>
+        <v>5299</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="N7" s="12">
         <f>ABS(I7-J7)*H7*K7</f>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -62,12 +62,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001D7A4C"/>
+      <color rgb="00C23A2B"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C23A2B"/>
+      <color rgb="001D7A4C"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>期货信号跟踪台 · 2026-10-29 （2026-10-30 早盘）</t>
+          <t>期货信号跟踪台 · 2026-10-30 收盘后</t>
         </is>
       </c>
     </row>
@@ -594,11 +594,11 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>入场价 ∓ 2×ATR(14)</t>
+          <t>入场价 ∓ 3×ATR(14)，之后按 3×ATR 移动</t>
         </is>
       </c>
     </row>
@@ -635,14 +635,14 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>规则（跟踪台 v2.4）</t>
+          <t>规则（跟踪台 v2.5）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>手数 = 向下取整(风险预算 ÷ (2×ATR×合约乘数))；计划风险 = |入场−止损|×手数×乘数。</t>
+          <t>手数 = 向下取整(风险预算 ÷ (3×ATR×合约乘数))；计划风险 = |入场−止损|×手数×乘数。</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>持有 3 个交易日；同向信号再出现=续持（重新计时）；反向信号先平后开；将军撤退/大将军转向当天收盘平。</t>
+          <t>入场须顺 5 日线（逆势观望）；止损按 3×ATR 移动，不限持有天数（最长 60 日）；同向信号=续持；反向先平后开；将军撤退/大将军转向当天收盘平。</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>宏观：美债10Y 5.02%（-2bp）｜2Y 4.69%（-2bp）｜10Y−2Y 33bp，牛陡｜美元 102.18（+0.04%）｜金 4034.19（-0.43%）｜银 52.46（-2.24%）｜铜 658.29（-1.33%）｜WTI 102.03（-0.73%）｜布油 110.67（-0.87%）</t>
+          <t>宏观：美债10Y 4.93%（+2bp）｜2Y 4.59%（+2bp）｜10Y−2Y 34bp，熊陡｜美元 101.97（+0.08%）｜金 3884.28（-3.65%）｜银 49.12（-6.23%）｜铜 650.48（-1.48%）｜WTI 102.91（+0.89%）｜布油 113.50（+2.44%）</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -799,22 +799,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>碳酸锂</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>FG</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -823,16 +823,16 @@
         </is>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>88360</v>
+        <v>865</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>100631.43</v>
+        <v>815.5</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>0.02</v>
@@ -856,24 +856,24 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>将军净-13.2%，4个将军；研报同向（多0/空5）</t>
+          <t>将军净3.6%，2个将军</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>碳酸锂</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>空</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -883,20 +883,20 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>开仓</t>
+          <t>续持</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>5299</v>
+        <v>88400</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>5050</v>
+        <v>100671.43</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>0.02</v>
@@ -915,29 +915,29 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>¼凯利超上限，取2%</t>
+          <t>续持原仓（2026-10-29开）</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>将军净4.7%，4个将军；研报同向（多3/空1）</t>
+          <t>将军净-13.7%，4个将军；研报同向（多0/空5）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>尿素</t>
+          <t>热轧卷板</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>HC</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>空</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -947,20 +947,20 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>开仓</t>
+          <t>续持</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>3193</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>3248.57</v>
+      </c>
+      <c r="I4" s="10" t="n">
         <v>10</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>1716</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>1670</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>20</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>0.01</v>
@@ -979,29 +979,29 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>组合风险已近10%，预算缩小</t>
+          <t>续持原仓（2026-10-26开）</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>将军净4.3%，4个将军</t>
+          <t>将军净-7.9%，4个将军</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>纸浆</t>
+          <t>尿素</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>4618</v>
+        <v>1725</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>4759.71</v>
+        <v>1679</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K5" s="12">
         <f>IF(F5="","",ABS(G5-H5)*F5*I5)</f>
@@ -1043,29 +1043,29 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>续持原仓（2026-10-26开）</t>
+          <t>续持原仓（2026-10-29开）</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>将军净-19.9%，4个将军</t>
+          <t>将军净4.1%，4个将军</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>热轧卷板</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>3193</v>
+        <v>5280</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>3248.57</v>
+        <v>5031</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K6" s="12">
         <f>IF(F6="","",ABS(G6-H6)*F6*I6)</f>
@@ -1107,24 +1107,24 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>续持原仓（2026-10-26开）</t>
+          <t>续持原仓（2026-10-29开）</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>将军净-7.7%，4个将军</t>
+          <t>将军净4.8%，4个将军；研报同向（多2/空0）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>白银</t>
+          <t>纸浆</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>AG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -1139,16 +1139,16 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>不做</t>
+          <t>观望</t>
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="16" t="n">
-        <v>12682</v>
+        <v>4614</v>
       </c>
       <c r="H7" s="16" t="n"/>
       <c r="I7" s="15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J7" s="17" t="n"/>
       <c r="K7" s="18">
@@ -1165,24 +1165,24 @@
       </c>
       <c r="N7" s="15" t="inlineStr">
         <is>
-          <t>重大事件前单方向≤7%，预算缩小</t>
+          <t>逆5日线（收盘在5日线上，不追空）</t>
         </is>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
-          <t>将军净-17.5%，4个将军</t>
+          <t>将军净-23.1%，4个将军；研报同向（多0/空2）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>豆粕</t>
+          <t>生猪</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -1202,11 +1202,11 @@
       </c>
       <c r="F8" s="15" t="n"/>
       <c r="G8" s="16" t="n">
-        <v>3161</v>
+        <v>9510</v>
       </c>
       <c r="H8" s="16" t="n"/>
       <c r="I8" s="15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J8" s="17" t="n"/>
       <c r="K8" s="18">
@@ -1223,29 +1223,29 @@
       </c>
       <c r="N8" s="15" t="inlineStr">
         <is>
-          <t>重大事件前单方向≤7%，预算缩小</t>
+          <t>1手风险14091元超过预算10000元</t>
         </is>
       </c>
       <c r="O8" s="15" t="inlineStr">
         <is>
-          <t>将军净-12.3%，4个将军；研报同向（多0/空5）</t>
+          <t>小品种独立额度；将军净-12.2%，4个将军</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>甲醇</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>空</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -1260,11 +1260,11 @@
       </c>
       <c r="F9" s="15" t="n"/>
       <c r="G9" s="16" t="n">
-        <v>3413</v>
+        <v>855.1799999999999</v>
       </c>
       <c r="H9" s="16" t="n"/>
       <c r="I9" s="15" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="J9" s="17" t="n"/>
       <c r="K9" s="18">
@@ -1281,35 +1281,151 @@
       </c>
       <c r="N9" s="15" t="inlineStr">
         <is>
+          <t>1手风险39129元超过预算20000元</t>
+        </is>
+      </c>
+      <c r="O9" s="15" t="inlineStr">
+        <is>
+          <t>将军净-4.1%，4个将军</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>锰硅</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>不做</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n">
+        <v>5890</v>
+      </c>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="18">
+        <f>IF(F10="","",ABS(G10-H10)*F10*I10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="19">
+        <f>IF(K10="","",K10/参数!$B$3)</f>
+        <v/>
+      </c>
+      <c r="M10" s="18">
+        <f>IF(F10="","",G10*F10*I10)</f>
+        <v/>
+      </c>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
           <t>组合风险已近10%，预算缩小</t>
         </is>
       </c>
-      <c r="O9" s="15" t="inlineStr">
-        <is>
-          <t>将军净10.5%，4个将军</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="I10" s="7" t="inlineStr">
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>将军净1.8%，2个将军；研报同向（多2/空0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>铁矿石</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>不做</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="16" t="n">
+        <v>672</v>
+      </c>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="18">
+        <f>IF(F11="","",ABS(G11-H11)*F11*I11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="19">
+        <f>IF(K11="","",K11/参数!$B$3)</f>
+        <v/>
+      </c>
+      <c r="M11" s="18">
+        <f>IF(F11="","",G11*F11*I11)</f>
+        <v/>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>组合风险已近10%，预算缩小</t>
+        </is>
+      </c>
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>将军净-1.1%，2个将军；研报同向（多1/空5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>合计（不含观察仓）</t>
         </is>
       </c>
-      <c r="J10" s="20">
-        <f>SUMIFS(J2:J9,$E$2:$E$9,"&lt;&gt;观察仓",$E$2:$E$9,"&lt;&gt;不做")</f>
-        <v/>
-      </c>
-      <c r="K10" s="21">
-        <f>SUMIFS(K2:K9,$E$2:$E$9,"&lt;&gt;观察仓",$E$2:$E$9,"&lt;&gt;不做")</f>
-        <v/>
-      </c>
-      <c r="L10" s="22">
-        <f>SUMIFS(L2:L9,$E$2:$E$9,"&lt;&gt;观察仓",$E$2:$E$9,"&lt;&gt;不做")</f>
-        <v/>
-      </c>
-      <c r="M10" s="21">
-        <f>SUMIFS(M2:M9,$E$2:$E$9,"&lt;&gt;观察仓",$E$2:$E$9,"&lt;&gt;不做")</f>
+      <c r="J12" s="20">
+        <f>SUMIFS(J2:J11,$E$2:$E$11,"&lt;&gt;观察仓",$E$2:$E$11,"&lt;&gt;不做")</f>
+        <v/>
+      </c>
+      <c r="K12" s="21">
+        <f>SUMIFS(K2:K11,$E$2:$E$11,"&lt;&gt;观察仓",$E$2:$E$11,"&lt;&gt;不做")</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
+        <f>SUMIFS(L2:L11,$E$2:$E$11,"&lt;&gt;观察仓",$E$2:$E$11,"&lt;&gt;不做")</f>
+        <v/>
+      </c>
+      <c r="M12" s="21">
+        <f>SUMIFS(M2:M11,$E$2:$E$11,"&lt;&gt;观察仓",$E$2:$E$11,"&lt;&gt;不做")</f>
         <v/>
       </c>
     </row>
@@ -1467,7 +1583,7 @@
           <t>HC</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -1500,7 +1616,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="11" t="n">
-        <v>3192</v>
+        <v>3170</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>0.01</v>
@@ -1550,7 +1666,7 @@
           <t>SP</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -1583,7 +1699,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>4604</v>
+        <v>4614</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>0.02</v>
@@ -1609,7 +1725,7 @@
         <v/>
       </c>
       <c r="S3" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1620,27 +1736,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪镍</t>
+          <t>碳酸锂</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1654,19 +1770,19 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>118130</v>
+        <v>88400</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>122783.85</v>
+        <v>100671.43</v>
       </c>
       <c r="K4" s="10" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>118090</v>
+        <v>88500</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0.02</v>
@@ -1692,7 +1808,7 @@
         <v/>
       </c>
       <c r="S4" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
@@ -1708,17 +1824,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>碳酸锂</t>
+          <t>尿素</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1728,31 +1844,31 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>建材</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待成交</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>88360</v>
+        <v>1725</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>100631.43</v>
+        <v>1679</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>88360</v>
+        <v>1736</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="N5" s="12">
         <f>ABS(I5-J5)*H5*K5</f>
@@ -1791,15 +1907,15 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>尿素</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>多</t>
         </is>
@@ -1811,31 +1927,31 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>建材</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待成交</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>1716</v>
+        <v>5280</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>1670</v>
+        <v>5031</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>1716</v>
+        <v>5290</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="N6" s="12">
         <f>ABS(I6-J6)*H6*K6</f>
@@ -1869,32 +1985,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>多</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>建材</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1903,19 +2019,19 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>5299</v>
+        <v>865</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>5050</v>
+        <v>815.5</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>5299</v>
+        <v>865</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0.02</v>
@@ -1998,7 +2114,7 @@
         <v>20</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>2595</v>
+        <v>2607</v>
       </c>
       <c r="M8" s="17" t="n">
         <v>0.01</v>
@@ -2024,7 +2140,7 @@
         <v/>
       </c>
       <c r="S8" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" s="15" t="inlineStr">
         <is>
@@ -2081,7 +2197,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>10217</v>
+        <v>10340</v>
       </c>
       <c r="M9" s="17" t="n">
         <v>0.01</v>
@@ -2107,7 +2223,7 @@
         <v/>
       </c>
       <c r="S9" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" s="15" t="inlineStr">
         <is>
@@ -2243,7 +2359,7 @@
           <t>化工</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>多</t>
         </is>
@@ -2263,7 +2379,7 @@
           <t>建材</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>多</t>
         </is>
@@ -2283,7 +2399,7 @@
           <t>有色</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -2303,7 +2419,7 @@
           <t>软商品</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -2323,7 +2439,7 @@
           <t>黑色</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -2355,7 +2471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2455,45 +2571,45 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>塑料</t>
+          <t>沪镍</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>空</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G2" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>9149</v>
+        <v>118130</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>9363</v>
+        <v>117190</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2" s="10" t="n">
         <v>20000</v>
@@ -2518,78 +2634,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>碳酸锂</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>94180</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>88360</v>
-      </c>
-      <c r="J3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L3" s="23">
-        <f>IF(E3="多",1,-1)*(I3-H3)*G3*J3</f>
-        <v/>
-      </c>
-      <c r="M3" s="24">
-        <f>L3/K3</f>
-        <v/>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>满3日</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>合计（实盘）</t>
         </is>
       </c>
-      <c r="L4" s="27">
-        <f>SUMIF(O2:O3,"否",L2:L3)</f>
+      <c r="L3" s="27">
+        <f>SUMIF(O2:O2,"否",L2:L2)</f>
         <v/>
       </c>
     </row>
@@ -2604,7 +2655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2704,45 +2755,45 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>塑料</t>
+          <t>沪镍</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>空</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G2" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>9149</v>
+        <v>118130</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>9363</v>
+        <v>117190</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2" s="10" t="n">
         <v>20000</v>
@@ -2769,7 +2820,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2779,17 +2830,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>碳酸锂</t>
+          <t>塑料</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2798,16 +2849,16 @@
         </is>
       </c>
       <c r="G3" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>94180</v>
+        <v>9149</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>88360</v>
+        <v>9363</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3" s="10" t="n">
         <v>20000</v>
@@ -2822,7 +2873,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>满3日</t>
+          <t>将军撤退</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -2834,25 +2885,25 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>螺纹</t>
+          <t>碳酸锂</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -2863,16 +2914,16 @@
         </is>
       </c>
       <c r="G4" s="10" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>3037</v>
+        <v>94180</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>3040</v>
+        <v>88360</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K4" s="10" t="n">
         <v>20000</v>
@@ -2887,7 +2938,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>将军撤退+大将军转向</t>
+          <t>满3日</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -2899,7 +2950,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2909,15 +2960,15 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>铁矿</t>
+          <t>螺纹</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -2928,19 +2979,19 @@
         </is>
       </c>
       <c r="G5" s="10" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>669</v>
+        <v>3037</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>664</v>
+        <v>3040</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="L5" s="23">
         <f>IF(E5="多",1,-1)*(I5-H5)*G5*J5</f>
@@ -2952,7 +3003,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>大将军转向</t>
+          <t>将军撤退+大将军转向</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -2964,27 +3015,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>燃料油</t>
+          <t>铁矿</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>FU</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>空</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2993,19 +3044,19 @@
         </is>
       </c>
       <c r="G6" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>5139</v>
+        <v>669</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>5295</v>
+        <v>664</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="L6" s="23">
         <f>IF(E6="多",1,-1)*(I6-H6)*G6*J6</f>
@@ -3017,7 +3068,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>将军撤退</t>
+          <t>大将军转向</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -3029,7 +3080,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3039,17 +3090,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>沪银</t>
+          <t>燃料油</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>AG</t>
+          <t>FU</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3058,16 +3109,16 @@
         </is>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>13608</v>
+        <v>5139</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>13040</v>
+        <v>5295</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>20000</v>
@@ -3082,7 +3133,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>将军撤退+大将军转向</t>
+          <t>将军撤退</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -3094,7 +3145,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3104,15 +3155,15 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>烧碱</t>
+          <t>沪银</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SH</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+          <t>AG</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -3123,19 +3174,19 @@
         </is>
       </c>
       <c r="G8" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>1682</v>
+        <v>13608</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>1512</v>
+        <v>13040</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="L8" s="23">
         <f>IF(E8="多",1,-1)*(I8-H8)*G8*J8</f>
@@ -3147,7 +3198,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>大将军转向</t>
+          <t>将军撤退+大将军转向</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -3159,7 +3210,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3169,15 +3220,15 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>硅铁</t>
+          <t>烧碱</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -3188,16 +3239,16 @@
         </is>
       </c>
       <c r="G9" s="10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>5812</v>
+        <v>1682</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>5828</v>
+        <v>1512</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>10000</v>
@@ -3212,7 +3263,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>满3日</t>
+          <t>大将军转向</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -3224,7 +3275,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3234,15 +3285,15 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>硅铁</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>FG</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -3253,16 +3304,16 @@
         </is>
       </c>
       <c r="G10" s="10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>863</v>
+        <v>5812</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>838</v>
+        <v>5828</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>10000</v>
@@ -3289,25 +3340,25 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>纯碱</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -3318,13 +3369,13 @@
         </is>
       </c>
       <c r="G11" s="10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>938</v>
+        <v>863</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>963</v>
+        <v>838</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>20</v>
@@ -3354,7 +3405,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3364,35 +3415,35 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>纸浆</t>
+          <t>纯碱</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G12" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>4728</v>
+        <v>938</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>4648</v>
+        <v>963</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>10000</v>
@@ -3417,67 +3468,67 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>沪锌</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>ZN</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>多</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>25495</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>25425</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" s="15" t="n">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>纸浆</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>4728</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>4648</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="23">
         <f>IF(E13="多",1,-1)*(I13-H13)*G13*J13</f>
         <v/>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="24">
         <f>L13/K13</f>
         <v/>
       </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>满3日</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3494,17 +3545,17 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>尿素</t>
+          <t>沪锌</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>ZN</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -3513,16 +3564,16 @@
         </is>
       </c>
       <c r="G14" s="15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>1694</v>
+        <v>25495</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>1682</v>
+        <v>25425</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>10000</v>
@@ -3559,12 +3610,12 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>白糖</t>
+          <t>尿素</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -3578,16 +3629,16 @@
         </is>
       </c>
       <c r="G15" s="15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>5379</v>
+        <v>1694</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>5383</v>
+        <v>1682</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K15" s="15" t="n">
         <v>10000</v>
@@ -3612,67 +3663,67 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>生猪</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>白糖</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>10215</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>9860</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K16" s="10" t="n">
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>5379</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>5383</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="L16" s="23">
+      <c r="L16" s="25">
         <f>IF(E16="多",1,-1)*(I16-H16)*G16*J16</f>
         <v/>
       </c>
-      <c r="M16" s="24">
+      <c r="M16" s="26">
         <f>L16/K16</f>
         <v/>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" s="15" t="inlineStr">
         <is>
           <t>满3日</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3689,15 +3740,15 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>鸡蛋</t>
+          <t>生猪</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+          <t>LH</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -3708,16 +3759,16 @@
         </is>
       </c>
       <c r="G17" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>3302</v>
+        <v>10215</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>3247</v>
+        <v>9860</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>10000</v>
@@ -3754,35 +3805,35 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>苯乙烯</t>
+          <t>鸡蛋</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>空</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G18" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>10235</v>
+        <v>3302</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>10672</v>
+        <v>3247</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>10000</v>
@@ -3819,35 +3870,35 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沥青</t>
+          <t>苯乙烯</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>BU</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G19" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>4397</v>
+        <v>10235</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>4533</v>
+        <v>10672</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>10000</v>
@@ -3872,307 +3923,307 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>沥青</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>BU</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>4397</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>4533</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L20" s="23">
+        <f>IF(E20="多",1,-1)*(I20-H20)*G20*J20</f>
+        <v/>
+      </c>
+      <c r="M20" s="24">
+        <f>L20/K20</f>
+        <v/>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>满3日</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>沪铝</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G21" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H21" s="16" t="n">
         <v>22970</v>
       </c>
-      <c r="I20" s="16" t="n">
+      <c r="I21" s="16" t="n">
         <v>23175</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J21" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="K20" s="15" t="n">
+      <c r="K21" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="L20" s="25">
-        <f>IF(E20="多",1,-1)*(I20-H20)*G20*J20</f>
-        <v/>
-      </c>
-      <c r="M20" s="26">
-        <f>L20/K20</f>
-        <v/>
-      </c>
-      <c r="N20" s="15" t="inlineStr">
+      <c r="L21" s="25">
+        <f>IF(E21="多",1,-1)*(I21-H21)*G21*J21</f>
+        <v/>
+      </c>
+      <c r="M21" s="26">
+        <f>L21/K21</f>
+        <v/>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
         <is>
           <t>满3日</t>
         </is>
       </c>
-      <c r="O20" s="15" t="inlineStr">
+      <c r="O21" s="15" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>燃料油</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>FU</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>多</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H22" s="11" t="n">
         <v>4516</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I22" s="11" t="n">
         <v>4911</v>
       </c>
-      <c r="J21" s="10" t="n">
+      <c r="J22" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="K21" s="10" t="n">
+      <c r="K22" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="L21" s="23">
-        <f>IF(E21="多",1,-1)*(I21-H21)*G21*J21</f>
-        <v/>
-      </c>
-      <c r="M21" s="24">
-        <f>L21/K21</f>
-        <v/>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="L22" s="23">
+        <f>IF(E22="多",1,-1)*(I22-H22)*G22*J22</f>
+        <v/>
+      </c>
+      <c r="M22" s="24">
+        <f>L22/K22</f>
+        <v/>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>满3日</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>菜粕</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>RM</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>多</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G23" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H23" s="16" t="n">
         <v>2345</v>
       </c>
-      <c r="I22" s="16" t="n">
+      <c r="I23" s="16" t="n">
         <v>2261</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J23" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="K22" s="15" t="n">
+      <c r="K23" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="L22" s="25">
-        <f>IF(E22="多",1,-1)*(I22-H22)*G22*J22</f>
-        <v/>
-      </c>
-      <c r="M22" s="26">
-        <f>L22/K22</f>
-        <v/>
-      </c>
-      <c r="N22" s="15" t="inlineStr">
+      <c r="L23" s="25">
+        <f>IF(E23="多",1,-1)*(I23-H23)*G23*J23</f>
+        <v/>
+      </c>
+      <c r="M23" s="26">
+        <f>L23/K23</f>
+        <v/>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
         <is>
           <t>止损</t>
         </is>
       </c>
-      <c r="O22" s="15" t="inlineStr">
+      <c r="O23" s="15" t="inlineStr">
         <is>
           <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>纯碱</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="H23" s="11" t="n">
-        <v>985</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>938</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="K23" s="10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L23" s="23">
-        <f>IF(E23="多",1,-1)*(I23-H23)*G23*J23</f>
-        <v/>
-      </c>
-      <c r="M23" s="24">
-        <f>L23/K23</f>
-        <v/>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>满3日</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沥青</t>
+          <t>纯碱</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>BU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>空</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G24" s="10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>4510</v>
+        <v>985</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>4397</v>
+        <v>938</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>10000</v>
@@ -4187,7 +4238,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>反向信号</t>
+          <t>满3日</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -4199,7 +4250,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -4209,15 +4260,15 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>聚丙烯</t>
+          <t>沥青</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
+          <t>BU</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>多</t>
         </is>
@@ -4228,16 +4279,16 @@
         </is>
       </c>
       <c r="G25" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>9382</v>
+        <v>4510</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>9320</v>
+        <v>4397</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>10000</v>
@@ -4252,7 +4303,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>满3日</t>
+          <t>反向信号</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -4274,17 +4325,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>生猪</t>
+          <t>聚丙烯</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>多</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -4293,16 +4344,16 @@
         </is>
       </c>
       <c r="G26" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>10885</v>
+        <v>9382</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>10215</v>
+        <v>9320</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>10000</v>
@@ -4334,20 +4385,20 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>生猪</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
+          <t>LH</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
@@ -4358,16 +4409,16 @@
         </is>
       </c>
       <c r="G27" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>4904</v>
+        <v>10885</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>4808</v>
+        <v>10215</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K27" s="10" t="n">
         <v>10000</v>
@@ -4392,78 +4443,143 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>4904</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>4808</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L28" s="23">
+        <f>IF(E28="多",1,-1)*(I28-H28)*G28*J28</f>
+        <v/>
+      </c>
+      <c r="M28" s="24">
+        <f>L28/K28</f>
+        <v/>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>满3日</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>沥青</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>BU</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>多</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="G29" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="16" t="n">
+      <c r="H29" s="16" t="n">
         <v>4532</v>
       </c>
-      <c r="I28" s="16" t="n">
+      <c r="I29" s="16" t="n">
         <v>4510</v>
       </c>
-      <c r="J28" s="15" t="n">
+      <c r="J29" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="K28" s="15" t="n">
+      <c r="K29" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="L28" s="25">
-        <f>IF(E28="多",1,-1)*(I28-H28)*G28*J28</f>
-        <v/>
-      </c>
-      <c r="M28" s="26">
-        <f>L28/K28</f>
-        <v/>
-      </c>
-      <c r="N28" s="15" t="inlineStr">
+      <c r="L29" s="25">
+        <f>IF(E29="多",1,-1)*(I29-H29)*G29*J29</f>
+        <v/>
+      </c>
+      <c r="M29" s="26">
+        <f>L29/K29</f>
+        <v/>
+      </c>
+      <c r="N29" s="15" t="inlineStr">
         <is>
           <t>满3日（更正：原记“跳空止损 −11.9%”是 10/14 主力由 BU2611 换到 BU2701 造成的假跌；入场价按换月价差 −579 由 5111 调为 4532）</t>
         </is>
       </c>
-      <c r="O28" s="15" t="inlineStr">
+      <c r="O29" s="15" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="K29" s="7" t="inlineStr">
+    <row r="30">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>合计（实盘）</t>
         </is>
       </c>
-      <c r="L29" s="27">
-        <f>SUMIF(O2:O28,"否",L2:L28)</f>
+      <c r="L30" s="27">
+        <f>SUMIF(O2:O29,"否",L2:L29)</f>
         <v/>
       </c>
     </row>
@@ -4478,7 +4594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4540,7 +4656,7 @@
         </is>
       </c>
       <c r="G3" s="34">
-        <f>COUNT(D3:D23)</f>
+        <f>COUNT(D3:D24)</f>
         <v/>
       </c>
     </row>
@@ -4565,7 +4681,7 @@
         </is>
       </c>
       <c r="G4" s="34">
-        <f>COUNTIF(D3:D23,"&gt;0")</f>
+        <f>COUNTIF(D3:D24,"&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -4615,7 +4731,7 @@
         </is>
       </c>
       <c r="G6" s="24">
-        <f>IFERROR(AVERAGEIF(D3:D23,"&gt;0"),0)</f>
+        <f>IFERROR(AVERAGEIF(D3:D24,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>
@@ -4640,7 +4756,7 @@
         </is>
       </c>
       <c r="G7" s="24">
-        <f>IFERROR(-AVERAGEIF(D3:D23,"&lt;=0"),0)</f>
+        <f>IFERROR(-AVERAGEIF(D3:D24,"&lt;=0"),0)</f>
         <v/>
       </c>
     </row>
@@ -4973,6 +5089,22 @@
       </c>
       <c r="D23" s="33" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪镍空 10-27</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>期货信号跟踪台 · 2026-10-30 收盘后</t>
+          <t>期货信号跟踪台 · 2026-10-30 （2026-11-01 早盘）</t>
         </is>
       </c>
     </row>
